--- a/JANUARY 2026/Outstanding Kitchen/KSP (Chicken) OUTSTANDING JANUARY 2026.xlsx
+++ b/JANUARY 2026/Outstanding Kitchen/KSP (Chicken) OUTSTANDING JANUARY 2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16600" windowHeight="17020"/>
+    <workbookView windowWidth="17160" windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="KSP (Chicken)" sheetId="1" r:id="rId1"/>
@@ -1167,7 +1167,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_E806AFC912C64647B993492A2712506F" descr="PHOTO-2026-01-06-16-53-01"/>
+        <xdr:cNvPr id="7" name="ID_E806AFC912C64647B993492A2712506F" descr="PHOTO-2026-01-06-16-53-01"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1205,7 +1205,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="ID_DFA83C72BD3B4AC3A29ACE2C63BC0A1F" descr="PHOTO-2026-01-13-11-18-35"/>
+        <xdr:cNvPr id="8" name="ID_DFA83C72BD3B4AC3A29ACE2C63BC0A1F" descr="PHOTO-2026-01-13-11-18-35"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1244,7 +1244,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="ID_0169FD9FA6344DBCBB91C391017F2227" descr="PHOTO-2026-01-20-12-48-38"/>
+        <xdr:cNvPr id="9" name="ID_0169FD9FA6344DBCBB91C391017F2227" descr="PHOTO-2026-01-20-12-48-38"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1282,7 +1282,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="ID_C5C97C2757E94DE793819BC945245CD3" descr="PHOTO-2026-01-23-17-29-57"/>
+        <xdr:cNvPr id="10" name="ID_C5C97C2757E94DE793819BC945245CD3" descr="PHOTO-2026-01-23-17-29-57"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1320,7 +1320,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="ID_08CC5F6BB55D4B81AFD3494C84754981" descr="PHOTO-2026-01-31-12-46-44"/>
+        <xdr:cNvPr id="11" name="ID_08CC5F6BB55D4B81AFD3494C84754981" descr="PHOTO-2026-01-31-12-46-44"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1711,8 +1711,8 @@
         <v>270000</v>
       </c>
       <c r="H4" s="21">
-        <f>SUM(G5:G6)</f>
-        <v>920200</v>
+        <f>SUM(G4:G6)</f>
+        <v>1190200</v>
       </c>
       <c r="K4" s="34"/>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="H7" s="27">
         <f>SUM(G7:G9)</f>
-        <v>894800</v>
+        <v>899500</v>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1" spans="1:8">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="26">
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="G9" s="26">
         <f t="shared" ref="G9:G18" si="1">D9*F9</f>
-        <v>164500</v>
+        <v>169200</v>
       </c>
       <c r="H9" s="29"/>
       <c r="K9" s="34"/>
@@ -2000,7 +2000,7 @@
       <c r="G19" s="26"/>
       <c r="H19" s="33">
         <f>SUM(H2:H18)</f>
-        <v>5102800</v>
+        <v>5377500</v>
       </c>
     </row>
   </sheetData>
